--- a/complementarios_lluvias/datos_mapa.xlsx
+++ b/complementarios_lluvias/datos_mapa.xlsx
@@ -790,7 +790,7 @@
     <t>1995</t>
   </si>
   <si>
-    <t>septiembre</t>
+    <t>octubre</t>
   </si>
 </sst>
 </file>
@@ -1209,7 +1209,7 @@
         <v>258</v>
       </c>
       <c r="I2">
-        <v>51.52</v>
+        <v>69.37333333333332</v>
       </c>
       <c r="J2">
         <v>39.554167</v>
@@ -1244,7 +1244,7 @@
         <v>258</v>
       </c>
       <c r="I3">
-        <v>49.98</v>
+        <v>62.40333333333333</v>
       </c>
       <c r="J3">
         <v>39.560833</v>
@@ -1279,7 +1279,7 @@
         <v>258</v>
       </c>
       <c r="I4">
-        <v>69.96428571428571</v>
+        <v>86.4148148148148</v>
       </c>
       <c r="J4">
         <v>39.748333</v>
@@ -1314,7 +1314,7 @@
         <v>258</v>
       </c>
       <c r="I5">
-        <v>61.19333333333334</v>
+        <v>76.69333333333334</v>
       </c>
       <c r="J5">
         <v>39.854722</v>
@@ -1349,7 +1349,7 @@
         <v>258</v>
       </c>
       <c r="I6">
-        <v>56.56666666666667</v>
+        <v>58.43666666666666</v>
       </c>
       <c r="J6">
         <v>38.876389</v>
@@ -1384,7 +1384,7 @@
         <v>258</v>
       </c>
       <c r="I7">
-        <v>2.166666666666667</v>
+        <v>9.856666666666666</v>
       </c>
       <c r="J7">
         <v>28.951944</v>
@@ -1419,7 +1419,7 @@
         <v>258</v>
       </c>
       <c r="I8">
-        <v>11.69</v>
+        <v>40.81666666666667</v>
       </c>
       <c r="J8">
         <v>28.633056</v>
@@ -1454,7 +1454,7 @@
         <v>258</v>
       </c>
       <c r="I9">
-        <v>2.416666666666667</v>
+        <v>7.703333333333333</v>
       </c>
       <c r="J9">
         <v>28.444722</v>
@@ -1489,7 +1489,7 @@
         <v>258</v>
       </c>
       <c r="I10">
-        <v>5.011111111111111</v>
+        <v>25.14444444444445</v>
       </c>
       <c r="J10">
         <v>28.031667</v>
@@ -1524,7 +1524,7 @@
         <v>258</v>
       </c>
       <c r="I11">
-        <v>3.583333333333333</v>
+        <v>11.47</v>
       </c>
       <c r="J11">
         <v>28.046944</v>
@@ -1559,7 +1559,7 @@
         <v>258</v>
       </c>
       <c r="I12">
-        <v>12.30333333333333</v>
+        <v>34.8</v>
       </c>
       <c r="J12">
         <v>28.308333</v>
@@ -1594,7 +1594,7 @@
         <v>258</v>
       </c>
       <c r="I13">
-        <v>16.07</v>
+        <v>46.52333333333333</v>
       </c>
       <c r="J13">
         <v>28.4775</v>
@@ -1629,7 +1629,7 @@
         <v>258</v>
       </c>
       <c r="I14">
-        <v>6.793333333333334</v>
+        <v>18.66333333333333</v>
       </c>
       <c r="J14">
         <v>28.463333</v>
@@ -1664,7 +1664,7 @@
         <v>258</v>
       </c>
       <c r="I15">
-        <v>9.06</v>
+        <v>15.96206896551724</v>
       </c>
       <c r="J15">
         <v>27.917778</v>
@@ -1699,7 +1699,7 @@
         <v>258</v>
       </c>
       <c r="I16">
-        <v>7</v>
+        <v>24.82777777777778</v>
       </c>
       <c r="J16">
         <v>28.075</v>
@@ -1734,7 +1734,7 @@
         <v>258</v>
       </c>
       <c r="I17">
-        <v>3.216666666666667</v>
+        <v>13.87</v>
       </c>
       <c r="J17">
         <v>27.818889</v>
@@ -1769,7 +1769,7 @@
         <v>258</v>
       </c>
       <c r="I18">
-        <v>74.93666666666667</v>
+        <v>74.7655172413793</v>
       </c>
       <c r="J18">
         <v>41.145</v>
@@ -1804,7 +1804,7 @@
         <v>258</v>
       </c>
       <c r="I19">
-        <v>73.52333333333333</v>
+        <v>69.17241379310344</v>
       </c>
       <c r="J19">
         <v>41.154167</v>
@@ -1839,7 +1839,7 @@
         <v>258</v>
       </c>
       <c r="I20">
-        <v>59.20769230769231</v>
+        <v>76.71923076923078</v>
       </c>
       <c r="J20">
         <v>41.72</v>
@@ -1874,7 +1874,7 @@
         <v>258</v>
       </c>
       <c r="I21">
-        <v>72.28666666666666</v>
+        <v>82.51333333333334</v>
       </c>
       <c r="J21">
         <v>41.594444</v>
@@ -1909,7 +1909,7 @@
         <v>258</v>
       </c>
       <c r="I22">
-        <v>74.88666666666667</v>
+        <v>91.28666666666666</v>
       </c>
       <c r="J22">
         <v>41.418333</v>
@@ -1944,7 +1944,7 @@
         <v>258</v>
       </c>
       <c r="I23">
-        <v>68.62608695652175</v>
+        <v>116.2181818181818</v>
       </c>
       <c r="J23">
         <v>41.967778</v>
@@ -1979,7 +1979,7 @@
         <v>258</v>
       </c>
       <c r="I24">
-        <v>51.35454545454545</v>
+        <v>80.22</v>
       </c>
       <c r="J24">
         <v>42.39</v>
@@ -2014,7 +2014,7 @@
         <v>258</v>
       </c>
       <c r="I25">
-        <v>132.1033333333333</v>
+        <v>166.6933333333333</v>
       </c>
       <c r="J25">
         <v>43.356944</v>
@@ -2081,7 +2081,7 @@
         <v>258</v>
       </c>
       <c r="I27">
-        <v>111.37</v>
+        <v>159.26</v>
       </c>
       <c r="J27">
         <v>43.306389</v>
@@ -2116,7 +2116,7 @@
         <v>258</v>
       </c>
       <c r="I28">
-        <v>73.24666666666667</v>
+        <v>111.1433333333333</v>
       </c>
       <c r="J28">
         <v>43.298056</v>
@@ -2151,7 +2151,7 @@
         <v>258</v>
       </c>
       <c r="I29">
-        <v>83.28333333333333</v>
+        <v>120.1833333333333</v>
       </c>
       <c r="J29">
         <v>43.423889</v>
@@ -2186,7 +2186,7 @@
         <v>258</v>
       </c>
       <c r="I30">
-        <v>88.89999999999999</v>
+        <v>113.0357142857143</v>
       </c>
       <c r="J30">
         <v>43.491111</v>
@@ -2221,7 +2221,7 @@
         <v>258</v>
       </c>
       <c r="I31">
-        <v>60.25</v>
+        <v>113.8818181818182</v>
       </c>
       <c r="J31">
         <v>43.523056</v>
@@ -2256,7 +2256,7 @@
         <v>258</v>
       </c>
       <c r="I32">
-        <v>55.17</v>
+        <v>101.87</v>
       </c>
       <c r="J32">
         <v>43.559722</v>
@@ -2291,7 +2291,7 @@
         <v>258</v>
       </c>
       <c r="I33">
-        <v>69.04074074074073</v>
+        <v>119.4222222222222</v>
       </c>
       <c r="J33">
         <v>43.566944</v>
@@ -2326,7 +2326,7 @@
         <v>258</v>
       </c>
       <c r="I34">
-        <v>66.10666666666667</v>
+        <v>98.51333333333334</v>
       </c>
       <c r="J34">
         <v>43.353333</v>
@@ -2393,7 +2393,7 @@
         <v>258</v>
       </c>
       <c r="I36">
-        <v>51.88333333333333</v>
+        <v>183.5</v>
       </c>
       <c r="J36">
         <v>43.476389</v>
@@ -2428,7 +2428,7 @@
         <v>258</v>
       </c>
       <c r="I37">
-        <v>63.55333333333333</v>
+        <v>130.34</v>
       </c>
       <c r="J37">
         <v>43.365833</v>
@@ -2463,7 +2463,7 @@
         <v>258</v>
       </c>
       <c r="I38">
-        <v>69.80666666666666</v>
+        <v>137.7066666666666</v>
       </c>
       <c r="J38">
         <v>43.306944</v>
@@ -2498,7 +2498,7 @@
         <v>258</v>
       </c>
       <c r="I39">
-        <v>106.6366666666667</v>
+        <v>225.8766666666667</v>
       </c>
       <c r="J39">
         <v>42.888056</v>
@@ -2533,7 +2533,7 @@
         <v>258</v>
       </c>
       <c r="I40">
-        <v>86.684</v>
+        <v>203.948</v>
       </c>
       <c r="J40">
         <v>42.582222</v>
@@ -2568,7 +2568,7 @@
         <v>258</v>
       </c>
       <c r="I41">
-        <v>95.264</v>
+        <v>223.5153846153846</v>
       </c>
       <c r="J41">
         <v>42.438333</v>
@@ -2603,7 +2603,7 @@
         <v>258</v>
       </c>
       <c r="I42">
-        <v>96.69259259259259</v>
+        <v>225.237037037037</v>
       </c>
       <c r="J42">
         <v>42.238611</v>
@@ -2638,7 +2638,7 @@
         <v>258</v>
       </c>
       <c r="I43">
-        <v>67.56538461538462</v>
+        <v>137.1961538461538</v>
       </c>
       <c r="J43">
         <v>43.111111</v>
@@ -2673,7 +2673,7 @@
         <v>258</v>
       </c>
       <c r="I44">
-        <v>48.90666666666667</v>
+        <v>81.41333333333334</v>
       </c>
       <c r="J44">
         <v>42.563889</v>
@@ -2708,7 +2708,7 @@
         <v>258</v>
       </c>
       <c r="I45">
-        <v>56.79310344827586</v>
+        <v>110.1766666666667</v>
       </c>
       <c r="J45">
         <v>42.325278</v>
@@ -2743,7 +2743,7 @@
         <v>258</v>
       </c>
       <c r="I46">
-        <v>32.94666666666667</v>
+        <v>55.34666666666667</v>
       </c>
       <c r="J46">
         <v>41.775</v>
@@ -2778,7 +2778,7 @@
         <v>258</v>
       </c>
       <c r="I47">
-        <v>38.26</v>
+        <v>60.15333333333334</v>
       </c>
       <c r="J47">
         <v>42.356944</v>
@@ -2813,7 +2813,7 @@
         <v>258</v>
       </c>
       <c r="I48">
-        <v>30.72666666666667</v>
+        <v>54.63</v>
       </c>
       <c r="J48">
         <v>41.640833</v>
@@ -2848,7 +2848,7 @@
         <v>258</v>
       </c>
       <c r="I49">
-        <v>30.02142857142857</v>
+        <v>52.92857142857143</v>
       </c>
       <c r="J49">
         <v>40.659167</v>
@@ -2883,7 +2883,7 @@
         <v>258</v>
       </c>
       <c r="I50">
-        <v>60.3625</v>
+        <v>133.1583333333333</v>
       </c>
       <c r="J50">
         <v>40.793056</v>
@@ -2918,7 +2918,7 @@
         <v>258</v>
       </c>
       <c r="I51">
-        <v>28.13181818181818</v>
+        <v>59.11739130434783</v>
       </c>
       <c r="J51">
         <v>40.945278</v>
@@ -2953,7 +2953,7 @@
         <v>258</v>
       </c>
       <c r="I52">
-        <v>32.28518518518518</v>
+        <v>55.05925925925926</v>
       </c>
       <c r="J52">
         <v>41.711944</v>
@@ -2988,7 +2988,7 @@
         <v>258</v>
       </c>
       <c r="I53">
-        <v>28.11</v>
+        <v>50.27</v>
       </c>
       <c r="J53">
         <v>41.515556</v>
@@ -3023,7 +3023,7 @@
         <v>258</v>
       </c>
       <c r="I54">
-        <v>32.37666666666667</v>
+        <v>45.56666666666667</v>
       </c>
       <c r="J54">
         <v>40.959444</v>
@@ -3058,7 +3058,7 @@
         <v>258</v>
       </c>
       <c r="I55">
-        <v>47.41999999999999</v>
+        <v>49.19</v>
       </c>
       <c r="J55">
         <v>40.841667</v>
@@ -3093,7 +3093,7 @@
         <v>258</v>
       </c>
       <c r="I56">
-        <v>24.13333333333333</v>
+        <v>51.34666666666667</v>
       </c>
       <c r="J56">
         <v>40.466667</v>
@@ -3128,7 +3128,7 @@
         <v>258</v>
       </c>
       <c r="I57">
-        <v>24.62</v>
+        <v>50.1</v>
       </c>
       <c r="J57">
         <v>40.488611</v>
@@ -3163,7 +3163,7 @@
         <v>258</v>
       </c>
       <c r="I58">
-        <v>36.35862068965518</v>
+        <v>75.54137931034482</v>
       </c>
       <c r="J58">
         <v>40.696111</v>
@@ -3198,7 +3198,7 @@
         <v>258</v>
       </c>
       <c r="I59">
-        <v>22.39</v>
+        <v>59.45666666666667</v>
       </c>
       <c r="J59">
         <v>40.411944</v>
@@ -3233,7 +3233,7 @@
         <v>258</v>
       </c>
       <c r="I60">
-        <v>23.96</v>
+        <v>59.72</v>
       </c>
       <c r="J60">
         <v>40.375556</v>
@@ -3268,7 +3268,7 @@
         <v>258</v>
       </c>
       <c r="I61">
-        <v>22.1</v>
+        <v>50.09333333333333</v>
       </c>
       <c r="J61">
         <v>40.299444</v>
@@ -3303,7 +3303,7 @@
         <v>258</v>
       </c>
       <c r="I62">
-        <v>18.04827586206897</v>
+        <v>48.23103448275862</v>
       </c>
       <c r="J62">
         <v>39.884722</v>
@@ -3338,7 +3338,7 @@
         <v>258</v>
       </c>
       <c r="I63">
-        <v>29.93571428571429</v>
+        <v>77.01785714285714</v>
       </c>
       <c r="J63">
         <v>39.471389</v>
@@ -3373,7 +3373,7 @@
         <v>258</v>
       </c>
       <c r="I64">
-        <v>28.3375</v>
+        <v>70.625</v>
       </c>
       <c r="J64">
         <v>38.950833</v>
@@ -3408,7 +3408,7 @@
         <v>258</v>
       </c>
       <c r="I65">
-        <v>26.42666666666667</v>
+        <v>53.30666666666666</v>
       </c>
       <c r="J65">
         <v>38.989167</v>
@@ -3443,7 +3443,7 @@
         <v>258</v>
       </c>
       <c r="I66">
-        <v>22.43333333333333</v>
+        <v>66.2</v>
       </c>
       <c r="J66">
         <v>38.883333</v>
@@ -3478,7 +3478,7 @@
         <v>258</v>
       </c>
       <c r="I67">
-        <v>25.9037037037037</v>
+        <v>67.9074074074074</v>
       </c>
       <c r="J67">
         <v>37.278333</v>
@@ -3513,7 +3513,7 @@
         <v>258</v>
       </c>
       <c r="I68">
-        <v>33.47142857142858</v>
+        <v>94.06666666666666</v>
       </c>
       <c r="J68">
         <v>35.888611</v>
@@ -3548,7 +3548,7 @@
         <v>258</v>
       </c>
       <c r="I69">
-        <v>26.38461538461538</v>
+        <v>54.22962962962963</v>
       </c>
       <c r="J69">
         <v>37.7775</v>
@@ -3583,7 +3583,7 @@
         <v>258</v>
       </c>
       <c r="I70">
-        <v>22.56333333333333</v>
+        <v>37.82</v>
       </c>
       <c r="J70">
         <v>37.137222</v>
@@ -3618,7 +3618,7 @@
         <v>258</v>
       </c>
       <c r="I71">
-        <v>19.39333333333333</v>
+        <v>40.49</v>
       </c>
       <c r="J71">
         <v>37.190278</v>
@@ -3653,7 +3653,7 @@
         <v>258</v>
       </c>
       <c r="I72">
-        <v>26.94333333333334</v>
+        <v>68.26666666666667</v>
       </c>
       <c r="J72">
         <v>37.416667</v>
@@ -3688,7 +3688,7 @@
         <v>258</v>
       </c>
       <c r="I73">
-        <v>26.79</v>
+        <v>67.27666666666667</v>
       </c>
       <c r="J73">
         <v>37.164444</v>
@@ -3723,7 +3723,7 @@
         <v>258</v>
       </c>
       <c r="I74">
-        <v>28.05217391304348</v>
+        <v>83.46956521739131</v>
       </c>
       <c r="J74">
         <v>36.638889</v>
@@ -3758,7 +3758,7 @@
         <v>258</v>
       </c>
       <c r="I75">
-        <v>26.975</v>
+        <v>72.21000000000001</v>
       </c>
       <c r="J75">
         <v>36.750556</v>
@@ -3793,7 +3793,7 @@
         <v>258</v>
       </c>
       <c r="I76">
-        <v>22.98965517241379</v>
+        <v>67.33571428571429</v>
       </c>
       <c r="J76">
         <v>36.499722</v>
@@ -3828,7 +3828,7 @@
         <v>258</v>
       </c>
       <c r="I77">
-        <v>15.84</v>
+        <v>39.96666666666667</v>
       </c>
       <c r="J77">
         <v>35.276389</v>
@@ -3863,7 +3863,7 @@
         <v>258</v>
       </c>
       <c r="I78">
-        <v>20.19333333333333</v>
+        <v>57.07</v>
       </c>
       <c r="J78">
         <v>36.666111</v>
@@ -3898,7 +3898,7 @@
         <v>258</v>
       </c>
       <c r="I79">
-        <v>13.88666666666667</v>
+        <v>26.66</v>
       </c>
       <c r="J79">
         <v>36.846389</v>
@@ -3933,7 +3933,7 @@
         <v>258</v>
       </c>
       <c r="I80">
-        <v>31.7037037037037</v>
+        <v>36.38518518518519</v>
       </c>
       <c r="J80">
         <v>38.001944</v>
@@ -3968,7 +3968,7 @@
         <v>258</v>
       </c>
       <c r="I81">
-        <v>29.33333333333333</v>
+        <v>34.40666666666667</v>
       </c>
       <c r="J81">
         <v>37.957778</v>
@@ -4003,7 +4003,7 @@
         <v>258</v>
       </c>
       <c r="I82">
-        <v>39.88666666666666</v>
+        <v>45.82333333333334</v>
       </c>
       <c r="J82">
         <v>38.282778</v>
@@ -4038,7 +4038,7 @@
         <v>258</v>
       </c>
       <c r="I83">
-        <v>55.48333333333333</v>
+        <v>47.44</v>
       </c>
       <c r="J83">
         <v>38.3725</v>
@@ -4073,7 +4073,7 @@
         <v>258</v>
       </c>
       <c r="I84">
-        <v>42.48333333333333</v>
+        <v>59.71333333333333</v>
       </c>
       <c r="J84">
         <v>40.067222</v>
@@ -4108,7 +4108,7 @@
         <v>258</v>
       </c>
       <c r="I85">
-        <v>33.66666666666666</v>
+        <v>41.75</v>
       </c>
       <c r="J85">
         <v>38.954167</v>
@@ -4143,7 +4143,7 @@
         <v>258</v>
       </c>
       <c r="I86">
-        <v>38.00357142857143</v>
+        <v>40.66785714285714</v>
       </c>
       <c r="J86">
         <v>39.005556</v>
@@ -4178,7 +4178,7 @@
         <v>258</v>
       </c>
       <c r="I87">
-        <v>35.696</v>
+        <v>46.716</v>
       </c>
       <c r="J87">
         <v>40.350833</v>
@@ -4213,7 +4213,7 @@
         <v>258</v>
       </c>
       <c r="I88">
-        <v>62.81666666666667</v>
+        <v>71.88333333333334</v>
       </c>
       <c r="J88">
         <v>39.485</v>
@@ -4248,7 +4248,7 @@
         <v>258</v>
       </c>
       <c r="I89">
-        <v>71.23999999999999</v>
+        <v>69.79666666666667</v>
       </c>
       <c r="J89">
         <v>39.957222</v>
@@ -4283,7 +4283,7 @@
         <v>258</v>
       </c>
       <c r="I90">
-        <v>40.93666666666666</v>
+        <v>70.17333333333333</v>
       </c>
       <c r="J90">
         <v>42.881944</v>
@@ -4350,7 +4350,7 @@
         <v>258</v>
       </c>
       <c r="I92">
-        <v>25.72333333333334</v>
+        <v>36.81666666666667</v>
       </c>
       <c r="J92">
         <v>42.452222</v>
@@ -4385,7 +4385,7 @@
         <v>258</v>
       </c>
       <c r="I93">
-        <v>43.75333333333333</v>
+        <v>68.05333333333334</v>
       </c>
       <c r="J93">
         <v>42.776944</v>
@@ -4420,7 +4420,7 @@
         <v>258</v>
       </c>
       <c r="I94">
-        <v>34.2421052631579</v>
+        <v>39.49444444444444</v>
       </c>
       <c r="J94">
         <v>40.926111</v>
@@ -4455,7 +4455,7 @@
         <v>258</v>
       </c>
       <c r="I95">
-        <v>37.22666666666667</v>
+        <v>37.60666666666667</v>
       </c>
       <c r="J95">
         <v>41.114444</v>
@@ -4490,7 +4490,7 @@
         <v>258</v>
       </c>
       <c r="I96">
-        <v>29.51</v>
+        <v>36.42666666666666</v>
       </c>
       <c r="J96">
         <v>41.660556</v>
@@ -4525,7 +4525,7 @@
         <v>258</v>
       </c>
       <c r="I97">
-        <v>40.57857142857143</v>
+        <v>43.3</v>
       </c>
       <c r="J97">
         <v>41.626111</v>
@@ -4560,7 +4560,7 @@
         <v>258</v>
       </c>
       <c r="I98">
-        <v>47.46206896551725</v>
+        <v>60.12413793103448</v>
       </c>
       <c r="J98">
         <v>42.084444</v>
@@ -4595,7 +4595,7 @@
         <v>258</v>
       </c>
       <c r="I99">
-        <v>62.21333333333334</v>
+        <v>77.91000000000001</v>
       </c>
       <c r="J99">
         <v>40.820278</v>

--- a/complementarios_lluvias/datos_mapa.xlsx
+++ b/complementarios_lluvias/datos_mapa.xlsx
@@ -790,7 +790,7 @@
     <t>1995</t>
   </si>
   <si>
-    <t>octubre</t>
+    <t>noviembre</t>
   </si>
 </sst>
 </file>
@@ -1209,7 +1209,7 @@
         <v>258</v>
       </c>
       <c r="I2">
-        <v>69.37333333333332</v>
+        <v>59.39666666666667</v>
       </c>
       <c r="J2">
         <v>39.554167</v>
@@ -1244,7 +1244,7 @@
         <v>258</v>
       </c>
       <c r="I3">
-        <v>62.40333333333333</v>
+        <v>55.03333333333333</v>
       </c>
       <c r="J3">
         <v>39.560833</v>
@@ -1279,7 +1279,7 @@
         <v>258</v>
       </c>
       <c r="I4">
-        <v>86.4148148148148</v>
+        <v>76.5551724137931</v>
       </c>
       <c r="J4">
         <v>39.748333</v>
@@ -1314,7 +1314,7 @@
         <v>258</v>
       </c>
       <c r="I5">
-        <v>76.69333333333334</v>
+        <v>86.90666666666667</v>
       </c>
       <c r="J5">
         <v>39.854722</v>
@@ -1349,7 +1349,7 @@
         <v>258</v>
       </c>
       <c r="I6">
-        <v>58.43666666666666</v>
+        <v>53.21333333333334</v>
       </c>
       <c r="J6">
         <v>38.876389</v>
@@ -1384,7 +1384,7 @@
         <v>258</v>
       </c>
       <c r="I7">
-        <v>9.856666666666666</v>
+        <v>14.67</v>
       </c>
       <c r="J7">
         <v>28.951944</v>
@@ -1419,7 +1419,7 @@
         <v>258</v>
       </c>
       <c r="I8">
-        <v>40.81666666666667</v>
+        <v>69.72666666666667</v>
       </c>
       <c r="J8">
         <v>28.633056</v>
@@ -1454,7 +1454,7 @@
         <v>258</v>
       </c>
       <c r="I9">
-        <v>7.703333333333333</v>
+        <v>13.23666666666667</v>
       </c>
       <c r="J9">
         <v>28.444722</v>
@@ -1489,7 +1489,7 @@
         <v>258</v>
       </c>
       <c r="I10">
-        <v>25.14444444444445</v>
+        <v>34.41111111111112</v>
       </c>
       <c r="J10">
         <v>28.031667</v>
@@ -1524,7 +1524,7 @@
         <v>258</v>
       </c>
       <c r="I11">
-        <v>11.47</v>
+        <v>26.29333333333334</v>
       </c>
       <c r="J11">
         <v>28.046944</v>
@@ -1559,7 +1559,7 @@
         <v>258</v>
       </c>
       <c r="I12">
-        <v>34.8</v>
+        <v>54.51333333333334</v>
       </c>
       <c r="J12">
         <v>28.308333</v>
@@ -1594,7 +1594,7 @@
         <v>258</v>
       </c>
       <c r="I13">
-        <v>46.52333333333333</v>
+        <v>81.05333333333333</v>
       </c>
       <c r="J13">
         <v>28.4775</v>
@@ -1629,7 +1629,7 @@
         <v>258</v>
       </c>
       <c r="I14">
-        <v>18.66333333333333</v>
+        <v>34.09666666666666</v>
       </c>
       <c r="J14">
         <v>28.463333</v>
@@ -1664,7 +1664,7 @@
         <v>258</v>
       </c>
       <c r="I15">
-        <v>15.96206896551724</v>
+        <v>21.74666666666667</v>
       </c>
       <c r="J15">
         <v>27.917778</v>
@@ -1699,7 +1699,7 @@
         <v>258</v>
       </c>
       <c r="I16">
-        <v>24.82777777777778</v>
+        <v>38.81764705882352</v>
       </c>
       <c r="J16">
         <v>28.075</v>
@@ -1734,7 +1734,7 @@
         <v>258</v>
       </c>
       <c r="I17">
-        <v>13.87</v>
+        <v>36.78666666666666</v>
       </c>
       <c r="J17">
         <v>27.818889</v>
@@ -1769,7 +1769,7 @@
         <v>258</v>
       </c>
       <c r="I18">
-        <v>74.7655172413793</v>
+        <v>52.94666666666667</v>
       </c>
       <c r="J18">
         <v>41.145</v>
@@ -1804,7 +1804,7 @@
         <v>258</v>
       </c>
       <c r="I19">
-        <v>69.17241379310344</v>
+        <v>56.38666666666667</v>
       </c>
       <c r="J19">
         <v>41.154167</v>
@@ -1839,7 +1839,7 @@
         <v>258</v>
       </c>
       <c r="I20">
-        <v>76.71923076923078</v>
+        <v>40.73846153846154</v>
       </c>
       <c r="J20">
         <v>41.72</v>
@@ -1874,7 +1874,7 @@
         <v>258</v>
       </c>
       <c r="I21">
-        <v>82.51333333333334</v>
+        <v>60.42666666666666</v>
       </c>
       <c r="J21">
         <v>41.594444</v>
@@ -1909,7 +1909,7 @@
         <v>258</v>
       </c>
       <c r="I22">
-        <v>91.28666666666666</v>
+        <v>65.58666666666667</v>
       </c>
       <c r="J22">
         <v>41.418333</v>
@@ -1944,7 +1944,7 @@
         <v>258</v>
       </c>
       <c r="I23">
-        <v>116.2181818181818</v>
+        <v>60.36086956521739</v>
       </c>
       <c r="J23">
         <v>41.967778</v>
@@ -1979,7 +1979,7 @@
         <v>258</v>
       </c>
       <c r="I24">
-        <v>80.22</v>
+        <v>48.2090909090909</v>
       </c>
       <c r="J24">
         <v>42.39</v>
@@ -2014,7 +2014,7 @@
         <v>258</v>
       </c>
       <c r="I25">
-        <v>166.6933333333333</v>
+        <v>188.0166666666667</v>
       </c>
       <c r="J25">
         <v>43.356944</v>
@@ -2081,7 +2081,7 @@
         <v>258</v>
       </c>
       <c r="I27">
-        <v>159.26</v>
+        <v>168.75</v>
       </c>
       <c r="J27">
         <v>43.306389</v>
@@ -2116,7 +2116,7 @@
         <v>258</v>
       </c>
       <c r="I28">
-        <v>111.1433333333333</v>
+        <v>146.6206896551724</v>
       </c>
       <c r="J28">
         <v>43.298056</v>
@@ -2151,7 +2151,7 @@
         <v>258</v>
       </c>
       <c r="I29">
-        <v>120.1833333333333</v>
+        <v>159.7033333333333</v>
       </c>
       <c r="J29">
         <v>43.423889</v>
@@ -2186,7 +2186,7 @@
         <v>258</v>
       </c>
       <c r="I30">
-        <v>113.0357142857143</v>
+        <v>167.5714285714286</v>
       </c>
       <c r="J30">
         <v>43.491111</v>
@@ -2221,7 +2221,7 @@
         <v>258</v>
       </c>
       <c r="I31">
-        <v>113.8818181818182</v>
+        <v>103.25</v>
       </c>
       <c r="J31">
         <v>43.523056</v>
@@ -2256,7 +2256,7 @@
         <v>258</v>
       </c>
       <c r="I32">
-        <v>101.87</v>
+        <v>128.75</v>
       </c>
       <c r="J32">
         <v>43.559722</v>
@@ -2291,7 +2291,7 @@
         <v>258</v>
       </c>
       <c r="I33">
-        <v>119.4222222222222</v>
+        <v>134.5333333333333</v>
       </c>
       <c r="J33">
         <v>43.566944</v>
@@ -2326,7 +2326,7 @@
         <v>258</v>
       </c>
       <c r="I34">
-        <v>98.51333333333334</v>
+        <v>114.69</v>
       </c>
       <c r="J34">
         <v>43.353333</v>
@@ -2393,7 +2393,7 @@
         <v>258</v>
       </c>
       <c r="I36">
-        <v>183.5</v>
+        <v>175.05</v>
       </c>
       <c r="J36">
         <v>43.476389</v>
@@ -2428,7 +2428,7 @@
         <v>258</v>
       </c>
       <c r="I37">
-        <v>130.34</v>
+        <v>138.05</v>
       </c>
       <c r="J37">
         <v>43.365833</v>
@@ -2463,7 +2463,7 @@
         <v>258</v>
       </c>
       <c r="I38">
-        <v>137.7066666666666</v>
+        <v>142.04</v>
       </c>
       <c r="J38">
         <v>43.306944</v>
@@ -2498,7 +2498,7 @@
         <v>258</v>
       </c>
       <c r="I39">
-        <v>225.8766666666667</v>
+        <v>216.7866666666667</v>
       </c>
       <c r="J39">
         <v>42.888056</v>
@@ -2533,7 +2533,7 @@
         <v>258</v>
       </c>
       <c r="I40">
-        <v>203.948</v>
+        <v>208.5</v>
       </c>
       <c r="J40">
         <v>42.582222</v>
@@ -2568,7 +2568,7 @@
         <v>258</v>
       </c>
       <c r="I41">
-        <v>223.5153846153846</v>
+        <v>222.0346153846154</v>
       </c>
       <c r="J41">
         <v>42.438333</v>
@@ -2603,7 +2603,7 @@
         <v>258</v>
       </c>
       <c r="I42">
-        <v>225.237037037037</v>
+        <v>249.0153846153846</v>
       </c>
       <c r="J42">
         <v>42.238611</v>
@@ -2638,7 +2638,7 @@
         <v>258</v>
       </c>
       <c r="I43">
-        <v>137.1961538461538</v>
+        <v>143.988</v>
       </c>
       <c r="J43">
         <v>43.111111</v>
@@ -2673,7 +2673,7 @@
         <v>258</v>
       </c>
       <c r="I44">
-        <v>81.41333333333334</v>
+        <v>82.2</v>
       </c>
       <c r="J44">
         <v>42.563889</v>
@@ -2708,7 +2708,7 @@
         <v>258</v>
       </c>
       <c r="I45">
-        <v>110.1766666666667</v>
+        <v>103.048275862069</v>
       </c>
       <c r="J45">
         <v>42.325278</v>
@@ -2743,7 +2743,7 @@
         <v>258</v>
       </c>
       <c r="I46">
-        <v>55.34666666666667</v>
+        <v>49.47666666666667</v>
       </c>
       <c r="J46">
         <v>41.775</v>
@@ -2778,7 +2778,7 @@
         <v>258</v>
       </c>
       <c r="I47">
-        <v>60.15333333333334</v>
+        <v>60.16666666666666</v>
       </c>
       <c r="J47">
         <v>42.356944</v>
@@ -2813,7 +2813,7 @@
         <v>258</v>
       </c>
       <c r="I48">
-        <v>54.63</v>
+        <v>52.16333333333333</v>
       </c>
       <c r="J48">
         <v>41.640833</v>
@@ -2848,7 +2848,7 @@
         <v>258</v>
       </c>
       <c r="I49">
-        <v>52.92857142857143</v>
+        <v>48.39285714285715</v>
       </c>
       <c r="J49">
         <v>40.659167</v>
@@ -2883,7 +2883,7 @@
         <v>258</v>
       </c>
       <c r="I50">
-        <v>133.1583333333333</v>
+        <v>173.6041666666667</v>
       </c>
       <c r="J50">
         <v>40.793056</v>
@@ -2918,7 +2918,7 @@
         <v>258</v>
       </c>
       <c r="I51">
-        <v>59.11739130434783</v>
+        <v>51.8</v>
       </c>
       <c r="J51">
         <v>40.945278</v>
@@ -2953,7 +2953,7 @@
         <v>258</v>
       </c>
       <c r="I52">
-        <v>55.05925925925926</v>
+        <v>49.22962962962963</v>
       </c>
       <c r="J52">
         <v>41.711944</v>
@@ -2988,7 +2988,7 @@
         <v>258</v>
       </c>
       <c r="I53">
-        <v>50.27</v>
+        <v>45.29</v>
       </c>
       <c r="J53">
         <v>41.515556</v>
@@ -3023,7 +3023,7 @@
         <v>258</v>
       </c>
       <c r="I54">
-        <v>45.56666666666667</v>
+        <v>40.44333333333334</v>
       </c>
       <c r="J54">
         <v>40.959444</v>
@@ -3058,7 +3058,7 @@
         <v>258</v>
       </c>
       <c r="I55">
-        <v>49.19</v>
+        <v>38.2</v>
       </c>
       <c r="J55">
         <v>40.841667</v>
@@ -3093,7 +3093,7 @@
         <v>258</v>
       </c>
       <c r="I56">
-        <v>51.34666666666667</v>
+        <v>49.29666666666667</v>
       </c>
       <c r="J56">
         <v>40.466667</v>
@@ -3128,7 +3128,7 @@
         <v>258</v>
       </c>
       <c r="I57">
-        <v>50.1</v>
+        <v>48.79666666666667</v>
       </c>
       <c r="J57">
         <v>40.488611</v>
@@ -3163,7 +3163,7 @@
         <v>258</v>
       </c>
       <c r="I58">
-        <v>75.54137931034482</v>
+        <v>78.10689655172413</v>
       </c>
       <c r="J58">
         <v>40.696111</v>
@@ -3198,7 +3198,7 @@
         <v>258</v>
       </c>
       <c r="I59">
-        <v>59.45666666666667</v>
+        <v>57.66333333333333</v>
       </c>
       <c r="J59">
         <v>40.411944</v>
@@ -3233,7 +3233,7 @@
         <v>258</v>
       </c>
       <c r="I60">
-        <v>59.72</v>
+        <v>56.72</v>
       </c>
       <c r="J60">
         <v>40.375556</v>
@@ -3268,7 +3268,7 @@
         <v>258</v>
       </c>
       <c r="I61">
-        <v>50.09333333333333</v>
+        <v>48.01666666666667</v>
       </c>
       <c r="J61">
         <v>40.299444</v>
@@ -3303,7 +3303,7 @@
         <v>258</v>
       </c>
       <c r="I62">
-        <v>48.23103448275862</v>
+        <v>39.34137931034483</v>
       </c>
       <c r="J62">
         <v>39.884722</v>
@@ -3338,7 +3338,7 @@
         <v>258</v>
       </c>
       <c r="I63">
-        <v>77.01785714285714</v>
+        <v>89.04285714285713</v>
       </c>
       <c r="J63">
         <v>39.471389</v>
@@ -3373,7 +3373,7 @@
         <v>258</v>
       </c>
       <c r="I64">
-        <v>70.625</v>
+        <v>25.5875</v>
       </c>
       <c r="J64">
         <v>38.950833</v>
@@ -3408,7 +3408,7 @@
         <v>258</v>
       </c>
       <c r="I65">
-        <v>53.30666666666666</v>
+        <v>45.14666666666667</v>
       </c>
       <c r="J65">
         <v>38.989167</v>
@@ -3443,7 +3443,7 @@
         <v>258</v>
       </c>
       <c r="I66">
-        <v>66.2</v>
+        <v>63.575</v>
       </c>
       <c r="J66">
         <v>38.883333</v>
@@ -3478,7 +3478,7 @@
         <v>258</v>
       </c>
       <c r="I67">
-        <v>67.9074074074074</v>
+        <v>78.65555555555557</v>
       </c>
       <c r="J67">
         <v>37.278333</v>
@@ -3513,7 +3513,7 @@
         <v>258</v>
       </c>
       <c r="I68">
-        <v>94.06666666666666</v>
+        <v>105.9714285714286</v>
       </c>
       <c r="J68">
         <v>35.888611</v>
@@ -3548,7 +3548,7 @@
         <v>258</v>
       </c>
       <c r="I69">
-        <v>54.22962962962963</v>
+        <v>61.66666666666666</v>
       </c>
       <c r="J69">
         <v>37.7775</v>
@@ -3583,7 +3583,7 @@
         <v>258</v>
       </c>
       <c r="I70">
-        <v>37.82</v>
+        <v>50.23</v>
       </c>
       <c r="J70">
         <v>37.137222</v>
@@ -3618,7 +3618,7 @@
         <v>258</v>
       </c>
       <c r="I71">
-        <v>40.49</v>
+        <v>54.06333333333334</v>
       </c>
       <c r="J71">
         <v>37.190278</v>
@@ -3653,7 +3653,7 @@
         <v>258</v>
       </c>
       <c r="I72">
-        <v>68.26666666666667</v>
+        <v>91.05666666666666</v>
       </c>
       <c r="J72">
         <v>37.416667</v>
@@ -3688,7 +3688,7 @@
         <v>258</v>
       </c>
       <c r="I73">
-        <v>67.27666666666667</v>
+        <v>85.71333333333334</v>
       </c>
       <c r="J73">
         <v>37.164444</v>
@@ -3723,7 +3723,7 @@
         <v>258</v>
       </c>
       <c r="I74">
-        <v>83.46956521739131</v>
+        <v>84.29565217391304</v>
       </c>
       <c r="J74">
         <v>36.638889</v>
@@ -3758,7 +3758,7 @@
         <v>258</v>
       </c>
       <c r="I75">
-        <v>72.21000000000001</v>
+        <v>96.10333333333332</v>
       </c>
       <c r="J75">
         <v>36.750556</v>
@@ -3793,7 +3793,7 @@
         <v>258</v>
       </c>
       <c r="I76">
-        <v>67.33571428571429</v>
+        <v>97.65714285714286</v>
       </c>
       <c r="J76">
         <v>36.499722</v>
@@ -3828,7 +3828,7 @@
         <v>258</v>
       </c>
       <c r="I77">
-        <v>39.96666666666667</v>
+        <v>57.27333333333333</v>
       </c>
       <c r="J77">
         <v>35.276389</v>
@@ -3863,7 +3863,7 @@
         <v>258</v>
       </c>
       <c r="I78">
-        <v>57.07</v>
+        <v>100.4566666666667</v>
       </c>
       <c r="J78">
         <v>36.666111</v>
@@ -3898,7 +3898,7 @@
         <v>258</v>
       </c>
       <c r="I79">
-        <v>26.66</v>
+        <v>28.38333333333333</v>
       </c>
       <c r="J79">
         <v>36.846389</v>
@@ -3933,7 +3933,7 @@
         <v>258</v>
       </c>
       <c r="I80">
-        <v>36.38518518518519</v>
+        <v>32.1037037037037</v>
       </c>
       <c r="J80">
         <v>38.001944</v>
@@ -3968,7 +3968,7 @@
         <v>258</v>
       </c>
       <c r="I81">
-        <v>34.40666666666667</v>
+        <v>33.34</v>
       </c>
       <c r="J81">
         <v>37.957778</v>
@@ -4003,7 +4003,7 @@
         <v>258</v>
       </c>
       <c r="I82">
-        <v>45.82333333333334</v>
+        <v>34.26</v>
       </c>
       <c r="J82">
         <v>38.282778</v>
@@ -4038,7 +4038,7 @@
         <v>258</v>
       </c>
       <c r="I83">
-        <v>47.44</v>
+        <v>35.85333333333333</v>
       </c>
       <c r="J83">
         <v>38.3725</v>
@@ -4073,7 +4073,7 @@
         <v>258</v>
       </c>
       <c r="I84">
-        <v>59.71333333333333</v>
+        <v>47.76333333333334</v>
       </c>
       <c r="J84">
         <v>40.067222</v>
@@ -4108,7 +4108,7 @@
         <v>258</v>
       </c>
       <c r="I85">
-        <v>41.75</v>
+        <v>34.38333333333333</v>
       </c>
       <c r="J85">
         <v>38.954167</v>
@@ -4143,7 +4143,7 @@
         <v>258</v>
       </c>
       <c r="I86">
-        <v>40.66785714285714</v>
+        <v>37.74285714285714</v>
       </c>
       <c r="J86">
         <v>39.005556</v>
@@ -4178,7 +4178,7 @@
         <v>258</v>
       </c>
       <c r="I87">
-        <v>46.716</v>
+        <v>21.976</v>
       </c>
       <c r="J87">
         <v>40.350833</v>
@@ -4213,7 +4213,7 @@
         <v>258</v>
       </c>
       <c r="I88">
-        <v>71.88333333333334</v>
+        <v>50.89666666666667</v>
       </c>
       <c r="J88">
         <v>39.485</v>
@@ -4248,7 +4248,7 @@
         <v>258</v>
       </c>
       <c r="I89">
-        <v>69.79666666666667</v>
+        <v>48.82333333333334</v>
       </c>
       <c r="J89">
         <v>39.957222</v>
@@ -4283,7 +4283,7 @@
         <v>258</v>
       </c>
       <c r="I90">
-        <v>70.17333333333333</v>
+        <v>90.86333333333333</v>
       </c>
       <c r="J90">
         <v>42.881944</v>
@@ -4350,7 +4350,7 @@
         <v>258</v>
       </c>
       <c r="I92">
-        <v>36.81666666666667</v>
+        <v>39.50666666666667</v>
       </c>
       <c r="J92">
         <v>42.452222</v>
@@ -4385,7 +4385,7 @@
         <v>258</v>
       </c>
       <c r="I93">
-        <v>68.05333333333334</v>
+        <v>75</v>
       </c>
       <c r="J93">
         <v>42.776944</v>
@@ -4420,7 +4420,7 @@
         <v>258</v>
       </c>
       <c r="I94">
-        <v>39.49444444444444</v>
+        <v>27.07222222222222</v>
       </c>
       <c r="J94">
         <v>40.926111</v>
@@ -4455,7 +4455,7 @@
         <v>258</v>
       </c>
       <c r="I95">
-        <v>37.60666666666667</v>
+        <v>33.85</v>
       </c>
       <c r="J95">
         <v>41.114444</v>
@@ -4490,7 +4490,7 @@
         <v>258</v>
       </c>
       <c r="I96">
-        <v>36.42666666666666</v>
+        <v>29.8</v>
       </c>
       <c r="J96">
         <v>41.660556</v>
@@ -4525,7 +4525,7 @@
         <v>258</v>
       </c>
       <c r="I97">
-        <v>43.3</v>
+        <v>30.23571428571429</v>
       </c>
       <c r="J97">
         <v>41.626111</v>
@@ -4560,7 +4560,7 @@
         <v>258</v>
       </c>
       <c r="I98">
-        <v>60.12413793103448</v>
+        <v>48.3551724137931</v>
       </c>
       <c r="J98">
         <v>42.084444</v>
@@ -4595,7 +4595,7 @@
         <v>258</v>
       </c>
       <c r="I99">
-        <v>77.91000000000001</v>
+        <v>59.87333333333333</v>
       </c>
       <c r="J99">
         <v>40.820278</v>

--- a/complementarios_lluvias/datos_mapa.xlsx
+++ b/complementarios_lluvias/datos_mapa.xlsx
@@ -790,7 +790,7 @@
     <t>1995</t>
   </si>
   <si>
-    <t>noviembre</t>
+    <t>diciembre</t>
   </si>
 </sst>
 </file>
@@ -1209,7 +1209,7 @@
         <v>258</v>
       </c>
       <c r="I2">
-        <v>59.39666666666667</v>
+        <v>48.19333333333334</v>
       </c>
       <c r="J2">
         <v>39.554167</v>
@@ -1244,7 +1244,7 @@
         <v>258</v>
       </c>
       <c r="I3">
-        <v>55.03333333333333</v>
+        <v>48.09333333333333</v>
       </c>
       <c r="J3">
         <v>39.560833</v>
@@ -1279,7 +1279,7 @@
         <v>258</v>
       </c>
       <c r="I4">
-        <v>76.5551724137931</v>
+        <v>71.27500000000001</v>
       </c>
       <c r="J4">
         <v>39.748333</v>
@@ -1314,7 +1314,7 @@
         <v>258</v>
       </c>
       <c r="I5">
-        <v>86.90666666666667</v>
+        <v>61.44333333333334</v>
       </c>
       <c r="J5">
         <v>39.854722</v>
@@ -1349,7 +1349,7 @@
         <v>258</v>
       </c>
       <c r="I6">
-        <v>53.21333333333334</v>
+        <v>50.55</v>
       </c>
       <c r="J6">
         <v>38.876389</v>
@@ -1384,7 +1384,7 @@
         <v>258</v>
       </c>
       <c r="I7">
-        <v>14.67</v>
+        <v>29.28</v>
       </c>
       <c r="J7">
         <v>28.951944</v>
@@ -1419,7 +1419,7 @@
         <v>258</v>
       </c>
       <c r="I8">
-        <v>69.72666666666667</v>
+        <v>80.18666666666667</v>
       </c>
       <c r="J8">
         <v>28.633056</v>
@@ -1454,7 +1454,7 @@
         <v>258</v>
       </c>
       <c r="I9">
-        <v>13.23666666666667</v>
+        <v>25.68333333333333</v>
       </c>
       <c r="J9">
         <v>28.444722</v>
@@ -1489,7 +1489,7 @@
         <v>258</v>
       </c>
       <c r="I10">
-        <v>34.41111111111112</v>
+        <v>55.34</v>
       </c>
       <c r="J10">
         <v>28.031667</v>
@@ -1524,7 +1524,7 @@
         <v>258</v>
       </c>
       <c r="I11">
-        <v>26.29333333333334</v>
+        <v>30.26</v>
       </c>
       <c r="J11">
         <v>28.046944</v>
@@ -1559,7 +1559,7 @@
         <v>258</v>
       </c>
       <c r="I12">
-        <v>54.51333333333334</v>
+        <v>67.88</v>
       </c>
       <c r="J12">
         <v>28.308333</v>
@@ -1594,7 +1594,7 @@
         <v>258</v>
       </c>
       <c r="I13">
-        <v>81.05333333333333</v>
+        <v>82.24333333333334</v>
       </c>
       <c r="J13">
         <v>28.4775</v>
@@ -1629,7 +1629,7 @@
         <v>258</v>
       </c>
       <c r="I14">
-        <v>34.09666666666666</v>
+        <v>43.20666666666667</v>
       </c>
       <c r="J14">
         <v>28.463333</v>
@@ -1664,7 +1664,7 @@
         <v>258</v>
       </c>
       <c r="I15">
-        <v>21.74666666666667</v>
+        <v>31.25666666666667</v>
       </c>
       <c r="J15">
         <v>27.917778</v>
@@ -1699,7 +1699,7 @@
         <v>258</v>
       </c>
       <c r="I16">
-        <v>38.81764705882352</v>
+        <v>38.06666666666667</v>
       </c>
       <c r="J16">
         <v>28.075</v>
@@ -1734,7 +1734,7 @@
         <v>258</v>
       </c>
       <c r="I17">
-        <v>36.78666666666666</v>
+        <v>44.39</v>
       </c>
       <c r="J17">
         <v>27.818889</v>
@@ -1769,7 +1769,7 @@
         <v>258</v>
       </c>
       <c r="I18">
-        <v>52.94666666666667</v>
+        <v>36.46666666666667</v>
       </c>
       <c r="J18">
         <v>41.145</v>
@@ -1804,7 +1804,7 @@
         <v>258</v>
       </c>
       <c r="I19">
-        <v>56.38666666666667</v>
+        <v>42.63</v>
       </c>
       <c r="J19">
         <v>41.154167</v>
@@ -1839,7 +1839,7 @@
         <v>258</v>
       </c>
       <c r="I20">
-        <v>40.73846153846154</v>
+        <v>38.17692307692307</v>
       </c>
       <c r="J20">
         <v>41.72</v>
@@ -1874,7 +1874,7 @@
         <v>258</v>
       </c>
       <c r="I21">
-        <v>60.42666666666666</v>
+        <v>46.74</v>
       </c>
       <c r="J21">
         <v>41.594444</v>
@@ -1909,7 +1909,7 @@
         <v>258</v>
       </c>
       <c r="I22">
-        <v>65.58666666666667</v>
+        <v>46.21666666666667</v>
       </c>
       <c r="J22">
         <v>41.418333</v>
@@ -1944,7 +1944,7 @@
         <v>258</v>
       </c>
       <c r="I23">
-        <v>60.36086956521739</v>
+        <v>69.88571428571429</v>
       </c>
       <c r="J23">
         <v>41.967778</v>
@@ -1979,7 +1979,7 @@
         <v>258</v>
       </c>
       <c r="I24">
-        <v>48.2090909090909</v>
+        <v>56.75</v>
       </c>
       <c r="J24">
         <v>42.39</v>
@@ -2014,7 +2014,7 @@
         <v>258</v>
       </c>
       <c r="I25">
-        <v>188.0166666666667</v>
+        <v>174.33</v>
       </c>
       <c r="J25">
         <v>43.356944</v>
@@ -2081,7 +2081,7 @@
         <v>258</v>
       </c>
       <c r="I27">
-        <v>168.75</v>
+        <v>151.1166666666667</v>
       </c>
       <c r="J27">
         <v>43.306389</v>
@@ -2116,7 +2116,7 @@
         <v>258</v>
       </c>
       <c r="I28">
-        <v>146.6206896551724</v>
+        <v>121.8620689655172</v>
       </c>
       <c r="J28">
         <v>43.298056</v>
@@ -2151,7 +2151,7 @@
         <v>258</v>
       </c>
       <c r="I29">
-        <v>159.7033333333333</v>
+        <v>118.4266666666667</v>
       </c>
       <c r="J29">
         <v>43.423889</v>
@@ -2186,7 +2186,7 @@
         <v>258</v>
       </c>
       <c r="I30">
-        <v>167.5714285714286</v>
+        <v>112.4071428571429</v>
       </c>
       <c r="J30">
         <v>43.491111</v>
@@ -2221,7 +2221,7 @@
         <v>258</v>
       </c>
       <c r="I31">
-        <v>103.25</v>
+        <v>99.85833333333333</v>
       </c>
       <c r="J31">
         <v>43.523056</v>
@@ -2256,7 +2256,7 @@
         <v>258</v>
       </c>
       <c r="I32">
-        <v>128.75</v>
+        <v>107.69</v>
       </c>
       <c r="J32">
         <v>43.559722</v>
@@ -2291,7 +2291,7 @@
         <v>258</v>
       </c>
       <c r="I33">
-        <v>134.5333333333333</v>
+        <v>118.6333333333333</v>
       </c>
       <c r="J33">
         <v>43.566944</v>
@@ -2326,7 +2326,7 @@
         <v>258</v>
       </c>
       <c r="I34">
-        <v>114.69</v>
+        <v>98.48</v>
       </c>
       <c r="J34">
         <v>43.353333</v>
@@ -2393,7 +2393,7 @@
         <v>258</v>
       </c>
       <c r="I36">
-        <v>175.05</v>
+        <v>139.8666666666667</v>
       </c>
       <c r="J36">
         <v>43.476389</v>
@@ -2428,7 +2428,7 @@
         <v>258</v>
       </c>
       <c r="I37">
-        <v>138.05</v>
+        <v>131.4466666666667</v>
       </c>
       <c r="J37">
         <v>43.365833</v>
@@ -2463,7 +2463,7 @@
         <v>258</v>
       </c>
       <c r="I38">
-        <v>142.04</v>
+        <v>144.7766666666667</v>
       </c>
       <c r="J38">
         <v>43.306944</v>
@@ -2498,7 +2498,7 @@
         <v>258</v>
       </c>
       <c r="I39">
-        <v>216.7866666666667</v>
+        <v>261.11</v>
       </c>
       <c r="J39">
         <v>42.888056</v>
@@ -2533,7 +2533,7 @@
         <v>258</v>
       </c>
       <c r="I40">
-        <v>208.5</v>
+        <v>195.792</v>
       </c>
       <c r="J40">
         <v>42.582222</v>
@@ -2568,7 +2568,7 @@
         <v>258</v>
       </c>
       <c r="I41">
-        <v>222.0346153846154</v>
+        <v>215.9384615384615</v>
       </c>
       <c r="J41">
         <v>42.438333</v>
@@ -2603,7 +2603,7 @@
         <v>258</v>
       </c>
       <c r="I42">
-        <v>249.0153846153846</v>
+        <v>257.1037037037037</v>
       </c>
       <c r="J42">
         <v>42.238611</v>
@@ -2638,7 +2638,7 @@
         <v>258</v>
       </c>
       <c r="I43">
-        <v>143.988</v>
+        <v>134.252</v>
       </c>
       <c r="J43">
         <v>43.111111</v>
@@ -2673,7 +2673,7 @@
         <v>258</v>
       </c>
       <c r="I44">
-        <v>82.2</v>
+        <v>89.27333333333334</v>
       </c>
       <c r="J44">
         <v>42.563889</v>
@@ -2708,7 +2708,7 @@
         <v>258</v>
       </c>
       <c r="I45">
-        <v>103.048275862069</v>
+        <v>111.5137931034483</v>
       </c>
       <c r="J45">
         <v>42.325278</v>
@@ -2743,7 +2743,7 @@
         <v>258</v>
       </c>
       <c r="I46">
-        <v>49.47666666666667</v>
+        <v>49.47</v>
       </c>
       <c r="J46">
         <v>41.775</v>
@@ -2778,7 +2778,7 @@
         <v>258</v>
       </c>
       <c r="I47">
-        <v>60.16666666666666</v>
+        <v>63.31666666666667</v>
       </c>
       <c r="J47">
         <v>42.356944</v>
@@ -2813,7 +2813,7 @@
         <v>258</v>
       </c>
       <c r="I48">
-        <v>52.16333333333333</v>
+        <v>53.47333333333334</v>
       </c>
       <c r="J48">
         <v>41.640833</v>
@@ -2848,7 +2848,7 @@
         <v>258</v>
       </c>
       <c r="I49">
-        <v>48.39285714285715</v>
+        <v>41.72142857142858</v>
       </c>
       <c r="J49">
         <v>40.659167</v>
@@ -2883,7 +2883,7 @@
         <v>258</v>
       </c>
       <c r="I50">
-        <v>173.6041666666667</v>
+        <v>166.2458333333333</v>
       </c>
       <c r="J50">
         <v>40.793056</v>
@@ -2918,7 +2918,7 @@
         <v>258</v>
       </c>
       <c r="I51">
-        <v>51.8</v>
+        <v>45.58260869565218</v>
       </c>
       <c r="J51">
         <v>40.945278</v>
@@ -2953,7 +2953,7 @@
         <v>258</v>
       </c>
       <c r="I52">
-        <v>49.22962962962963</v>
+        <v>49.00740740740741</v>
       </c>
       <c r="J52">
         <v>41.711944</v>
@@ -2988,7 +2988,7 @@
         <v>258</v>
       </c>
       <c r="I53">
-        <v>45.29</v>
+        <v>46.29666666666667</v>
       </c>
       <c r="J53">
         <v>41.515556</v>
@@ -3023,7 +3023,7 @@
         <v>258</v>
       </c>
       <c r="I54">
-        <v>40.44333333333334</v>
+        <v>41.47333333333334</v>
       </c>
       <c r="J54">
         <v>40.959444</v>
@@ -3058,7 +3058,7 @@
         <v>258</v>
       </c>
       <c r="I55">
-        <v>38.2</v>
+        <v>36.31034482758621</v>
       </c>
       <c r="J55">
         <v>40.841667</v>
@@ -3093,7 +3093,7 @@
         <v>258</v>
       </c>
       <c r="I56">
-        <v>49.29666666666667</v>
+        <v>42.26</v>
       </c>
       <c r="J56">
         <v>40.466667</v>
@@ -3128,7 +3128,7 @@
         <v>258</v>
       </c>
       <c r="I57">
-        <v>48.79666666666667</v>
+        <v>41.26333333333334</v>
       </c>
       <c r="J57">
         <v>40.488611</v>
@@ -3163,7 +3163,7 @@
         <v>258</v>
       </c>
       <c r="I58">
-        <v>78.10689655172413</v>
+        <v>68.60357142857143</v>
       </c>
       <c r="J58">
         <v>40.696111</v>
@@ -3198,7 +3198,7 @@
         <v>258</v>
       </c>
       <c r="I59">
-        <v>57.66333333333333</v>
+        <v>51.1</v>
       </c>
       <c r="J59">
         <v>40.411944</v>
@@ -3233,7 +3233,7 @@
         <v>258</v>
       </c>
       <c r="I60">
-        <v>56.72</v>
+        <v>52.94666666666667</v>
       </c>
       <c r="J60">
         <v>40.375556</v>
@@ -3268,7 +3268,7 @@
         <v>258</v>
       </c>
       <c r="I61">
-        <v>48.01666666666667</v>
+        <v>44.80333333333333</v>
       </c>
       <c r="J61">
         <v>40.299444</v>
@@ -3303,7 +3303,7 @@
         <v>258</v>
       </c>
       <c r="I62">
-        <v>39.34137931034483</v>
+        <v>40.86206896551724</v>
       </c>
       <c r="J62">
         <v>39.884722</v>
@@ -3338,7 +3338,7 @@
         <v>258</v>
       </c>
       <c r="I63">
-        <v>89.04285714285713</v>
+        <v>77.41034482758621</v>
       </c>
       <c r="J63">
         <v>39.471389</v>
@@ -3373,7 +3373,7 @@
         <v>258</v>
       </c>
       <c r="I64">
-        <v>25.5875</v>
+        <v>63.05</v>
       </c>
       <c r="J64">
         <v>38.950833</v>
@@ -3408,7 +3408,7 @@
         <v>258</v>
       </c>
       <c r="I65">
-        <v>45.14666666666667</v>
+        <v>58.78666666666666</v>
       </c>
       <c r="J65">
         <v>38.989167</v>
@@ -3443,7 +3443,7 @@
         <v>258</v>
       </c>
       <c r="I66">
-        <v>63.575</v>
+        <v>71.77499999999999</v>
       </c>
       <c r="J66">
         <v>38.883333</v>
@@ -3478,7 +3478,7 @@
         <v>258</v>
       </c>
       <c r="I67">
-        <v>78.65555555555557</v>
+        <v>99.37777777777777</v>
       </c>
       <c r="J67">
         <v>37.278333</v>
@@ -3513,7 +3513,7 @@
         <v>258</v>
       </c>
       <c r="I68">
-        <v>105.9714285714286</v>
+        <v>181.7166666666667</v>
       </c>
       <c r="J68">
         <v>35.888611</v>
@@ -3548,7 +3548,7 @@
         <v>258</v>
       </c>
       <c r="I69">
-        <v>61.66666666666666</v>
+        <v>75.06923076923077</v>
       </c>
       <c r="J69">
         <v>37.7775</v>
@@ -3583,7 +3583,7 @@
         <v>258</v>
       </c>
       <c r="I70">
-        <v>50.23</v>
+        <v>50.19</v>
       </c>
       <c r="J70">
         <v>37.137222</v>
@@ -3618,7 +3618,7 @@
         <v>258</v>
       </c>
       <c r="I71">
-        <v>54.06333333333334</v>
+        <v>56.57333333333334</v>
       </c>
       <c r="J71">
         <v>37.190278</v>
@@ -3653,7 +3653,7 @@
         <v>258</v>
       </c>
       <c r="I72">
-        <v>91.05666666666666</v>
+        <v>99</v>
       </c>
       <c r="J72">
         <v>37.416667</v>
@@ -3688,7 +3688,7 @@
         <v>258</v>
       </c>
       <c r="I73">
-        <v>85.71333333333334</v>
+        <v>94.06333333333333</v>
       </c>
       <c r="J73">
         <v>37.164444</v>
@@ -3723,7 +3723,7 @@
         <v>258</v>
       </c>
       <c r="I74">
-        <v>84.29565217391304</v>
+        <v>103.8173913043478</v>
       </c>
       <c r="J74">
         <v>36.638889</v>
@@ -3758,7 +3758,7 @@
         <v>258</v>
       </c>
       <c r="I75">
-        <v>96.10333333333332</v>
+        <v>108.7266666666667</v>
       </c>
       <c r="J75">
         <v>36.750556</v>
@@ -3793,7 +3793,7 @@
         <v>258</v>
       </c>
       <c r="I76">
-        <v>97.65714285714286</v>
+        <v>92.28571428571429</v>
       </c>
       <c r="J76">
         <v>36.499722</v>
@@ -3828,7 +3828,7 @@
         <v>258</v>
       </c>
       <c r="I77">
-        <v>57.27333333333333</v>
+        <v>49.76333333333334</v>
       </c>
       <c r="J77">
         <v>35.276389</v>
@@ -3863,7 +3863,7 @@
         <v>258</v>
       </c>
       <c r="I78">
-        <v>100.4566666666667</v>
+        <v>99.58</v>
       </c>
       <c r="J78">
         <v>36.666111</v>
@@ -3898,7 +3898,7 @@
         <v>258</v>
       </c>
       <c r="I79">
-        <v>28.38333333333333</v>
+        <v>30.07666666666667</v>
       </c>
       <c r="J79">
         <v>36.846389</v>
@@ -3933,7 +3933,7 @@
         <v>258</v>
       </c>
       <c r="I80">
-        <v>32.1037037037037</v>
+        <v>28.62222222222222</v>
       </c>
       <c r="J80">
         <v>38.001944</v>
@@ -3968,7 +3968,7 @@
         <v>258</v>
       </c>
       <c r="I81">
-        <v>33.34</v>
+        <v>24.55</v>
       </c>
       <c r="J81">
         <v>37.957778</v>
@@ -4003,7 +4003,7 @@
         <v>258</v>
       </c>
       <c r="I82">
-        <v>34.26</v>
+        <v>21.4551724137931</v>
       </c>
       <c r="J82">
         <v>38.282778</v>
@@ -4038,7 +4038,7 @@
         <v>258</v>
       </c>
       <c r="I83">
-        <v>35.85333333333333</v>
+        <v>25.43333333333333</v>
       </c>
       <c r="J83">
         <v>38.3725</v>
@@ -4073,7 +4073,7 @@
         <v>258</v>
       </c>
       <c r="I84">
-        <v>47.76333333333334</v>
+        <v>57.49666666666667</v>
       </c>
       <c r="J84">
         <v>40.067222</v>
@@ -4108,7 +4108,7 @@
         <v>258</v>
       </c>
       <c r="I85">
-        <v>34.38333333333333</v>
+        <v>31.19333333333333</v>
       </c>
       <c r="J85">
         <v>38.954167</v>
@@ -4143,7 +4143,7 @@
         <v>258</v>
       </c>
       <c r="I86">
-        <v>37.74285714285714</v>
+        <v>32.07037037037037</v>
       </c>
       <c r="J86">
         <v>39.005556</v>
@@ -4178,7 +4178,7 @@
         <v>258</v>
       </c>
       <c r="I87">
-        <v>21.976</v>
+        <v>19.18</v>
       </c>
       <c r="J87">
         <v>40.350833</v>
@@ -4213,7 +4213,7 @@
         <v>258</v>
       </c>
       <c r="I88">
-        <v>50.89666666666667</v>
+        <v>47.64666666666667</v>
       </c>
       <c r="J88">
         <v>39.485</v>
@@ -4248,7 +4248,7 @@
         <v>258</v>
       </c>
       <c r="I89">
-        <v>48.82333333333334</v>
+        <v>42.24</v>
       </c>
       <c r="J89">
         <v>39.957222</v>
@@ -4283,7 +4283,7 @@
         <v>258</v>
       </c>
       <c r="I90">
-        <v>90.86333333333333</v>
+        <v>81.45</v>
       </c>
       <c r="J90">
         <v>42.881944</v>
@@ -4350,7 +4350,7 @@
         <v>258</v>
       </c>
       <c r="I92">
-        <v>39.50666666666667</v>
+        <v>37.57333333333334</v>
       </c>
       <c r="J92">
         <v>42.452222</v>
@@ -4385,7 +4385,7 @@
         <v>258</v>
       </c>
       <c r="I93">
-        <v>75</v>
+        <v>72.12666666666668</v>
       </c>
       <c r="J93">
         <v>42.776944</v>
@@ -4420,7 +4420,7 @@
         <v>258</v>
       </c>
       <c r="I94">
-        <v>27.07222222222222</v>
+        <v>25.72777777777778</v>
       </c>
       <c r="J94">
         <v>40.926111</v>
@@ -4455,7 +4455,7 @@
         <v>258</v>
       </c>
       <c r="I95">
-        <v>33.85</v>
+        <v>26.53666666666667</v>
       </c>
       <c r="J95">
         <v>41.114444</v>
@@ -4490,7 +4490,7 @@
         <v>258</v>
       </c>
       <c r="I96">
-        <v>29.8</v>
+        <v>21.41</v>
       </c>
       <c r="J96">
         <v>41.660556</v>
@@ -4525,7 +4525,7 @@
         <v>258</v>
       </c>
       <c r="I97">
-        <v>30.23571428571429</v>
+        <v>24.54642857142857</v>
       </c>
       <c r="J97">
         <v>41.626111</v>
@@ -4560,7 +4560,7 @@
         <v>258</v>
       </c>
       <c r="I98">
-        <v>48.3551724137931</v>
+        <v>43.51724137931034</v>
       </c>
       <c r="J98">
         <v>42.084444</v>
@@ -4595,7 +4595,7 @@
         <v>258</v>
       </c>
       <c r="I99">
-        <v>59.87333333333333</v>
+        <v>40.66666666666666</v>
       </c>
       <c r="J99">
         <v>40.820278</v>
